--- a/ecosysem/db/Excels/DeltaG0f.xlsx
+++ b/ecosysem/db/Excels/DeltaG0f.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C92760-58BB-4302-A283-ED107AA80035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1177444-35AF-4C5D-A40E-15A0DADA2D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4044" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
     <sheet name="DeltaG" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>IUPAC</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>N2</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>CH1.8O0.5N0.2</t>
   </si>
 </sst>
 </file>
@@ -736,17 +742,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC731D4-E3C1-4B64-BF1D-C3C9432561A9}">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -780,7 +786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -797,7 +803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -814,7 +820,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -831,7 +837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -848,7 +854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -865,7 +871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -882,7 +888,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -899,7 +905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -916,7 +922,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -933,7 +939,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -950,7 +956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -967,7 +973,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -984,7 +990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1001,7 +1007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1035,7 +1041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1086,7 +1092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1103,7 +1109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1120,7 +1126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1137,7 +1143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -1171,7 +1177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1205,7 +1211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -1222,7 +1228,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1239,7 +1245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -1256,7 +1262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1273,7 +1279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -1290,7 +1296,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -1307,7 +1313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -1324,7 +1330,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -1341,7 +1347,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -1358,7 +1364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -1375,7 +1381,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -1392,7 +1398,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -1409,7 +1415,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -1426,7 +1432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1443,7 +1449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>72</v>
       </c>
@@ -1460,7 +1466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>72</v>
       </c>
@@ -1477,7 +1483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -1494,7 +1500,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -1511,7 +1517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>77</v>
       </c>
@@ -1545,7 +1551,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -1562,7 +1568,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>81</v>
       </c>
@@ -1579,7 +1585,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -1596,7 +1602,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -1613,7 +1619,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -1630,7 +1636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>88</v>
       </c>
@@ -1645,6 +1651,23 @@
       </c>
       <c r="E53" s="3" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" s="3">
+        <v>-67</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/ecosysem/db/Excels/DeltaG0f.xlsx
+++ b/ecosysem/db/Excels/DeltaG0f.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1177444-35AF-4C5D-A40E-15A0DADA2D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258334DA-D98A-461F-BB66-FD390992114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="14175" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
     <sheet name="DeltaG" sheetId="1" r:id="rId1"/>

--- a/ecosysem/db/Excels/DeltaG0f.xlsx
+++ b/ecosysem/db/Excels/DeltaG0f.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258334DA-D98A-461F-BB66-FD390992114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F991E152-3A58-4A97-9ED8-35F46CF01067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14175" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="-3795" yWindow="-20475" windowWidth="28800" windowHeight="15345" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
     <sheet name="DeltaG" sheetId="1" r:id="rId1"/>
@@ -1545,7 +1545,7 @@
         <v>69</v>
       </c>
       <c r="D47" s="3">
-        <v>-424.7</v>
+        <v>-361.4</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>76</v>
